--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1597-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1597-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2BE52427-30AB-45A4-89A0-6F2EDCEC1833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C7CA98A0-8A00-4FAF-9BA3-126B3B08321C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{19EECBBA-004A-43AF-ADA7-84592766B650}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{6E0D8D80-4CB1-4C1C-87B0-053843284B4F}"/>
   </bookViews>
   <sheets>
     <sheet name="1597-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1550,25 +1550,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F2090D8-A136-4532-96D6-F9A19E004E67}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C756630F-78A4-40E3-AC3A-DF421390C86C}">
   <dimension ref="A1:X33"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11.125" customWidth="1"/>
-    <col min="4" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="9" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
@@ -1602,7 +1602,7 @@
       <c r="W1" s="33"/>
       <c r="X1" s="25"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
@@ -1638,7 +1638,7 @@
       <c r="W2" s="35"/>
       <c r="X2" s="36"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="26" t="s">
         <v>2</v>
       </c>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="X3" s="39"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="28"/>
       <c r="B4" s="29"/>
       <c r="C4" s="7"/>
@@ -1758,7 +1758,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="40">
         <v>2024</v>
       </c>
@@ -1830,7 +1830,7 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1904,7 +1904,7 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1978,7 +1978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="42">
         <v>2023</v>
       </c>
@@ -2050,7 +2050,7 @@
         <v>1.29</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2124,7 +2124,7 @@
         <v>1.29</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>29</v>
       </c>
@@ -2198,7 +2198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="40">
         <v>2022</v>
       </c>
@@ -2270,7 +2270,7 @@
         <v>3.27</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>29</v>
       </c>
@@ -2344,7 +2344,7 @@
         <v>3.27</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>29</v>
       </c>
@@ -2418,7 +2418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>29</v>
       </c>
@@ -2492,7 +2492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="44">
         <v>2021</v>
       </c>
@@ -2564,7 +2564,7 @@
         <v>3.79</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="46"/>
       <c r="B16" s="47"/>
       <c r="C16" s="20" t="s">
@@ -2592,7 +2592,7 @@
       <c r="W16" s="53"/>
       <c r="X16" s="49"/>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="50" t="s">
         <v>29</v>
       </c>
@@ -2666,7 +2666,7 @@
         <v>3.79</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="51"/>
       <c r="B18" s="51"/>
       <c r="C18" s="22" t="s">
@@ -2694,7 +2694,7 @@
       <c r="W18" s="53"/>
       <c r="X18" s="49"/>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="16" t="s">
         <v>29</v>
       </c>
@@ -2768,7 +2768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="40">
         <v>2020</v>
       </c>
@@ -2840,7 +2840,7 @@
         <v>1.87</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>29</v>
       </c>
@@ -2914,7 +2914,7 @@
         <v>1.87</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
         <v>29</v>
       </c>
@@ -2988,7 +2988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="42">
         <v>2019</v>
       </c>
@@ -3060,7 +3060,7 @@
         <v>2.0499999999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="40">
         <v>2018</v>
       </c>
@@ -3132,7 +3132,7 @@
         <v>2.77</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="42">
         <v>2017</v>
       </c>
@@ -3204,7 +3204,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="40">
         <v>2016</v>
       </c>
@@ -3276,7 +3276,7 @@
         <v>3.26</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="42">
         <v>2015</v>
       </c>
@@ -3348,7 +3348,7 @@
         <v>4.1100000000000003</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="40">
         <v>2014</v>
       </c>
@@ -3420,7 +3420,7 @@
         <v>2.31</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="42">
         <v>2013</v>
       </c>
@@ -3492,7 +3492,7 @@
         <v>2.48</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="40">
         <v>2012</v>
       </c>
@@ -3564,7 +3564,7 @@
         <v>1.95</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="42">
         <v>2011</v>
       </c>
@@ -3636,7 +3636,7 @@
         <v>5.13</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="40">
         <v>2010</v>
       </c>
@@ -3708,7 +3708,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="42" t="s">
         <v>54</v>
       </c>
